--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.5733802318572998</v>
+        <v>1.7040019035339355</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.7040019035339355</v>
+        <v>1.5787780284881592</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.5787780284881592</v>
+        <v>1.5190589427947998</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.5190589427947998</v>
+        <v>1.5398890972137451</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.5398890972137451</v>
+        <v>1.308241844177246</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.308241844177246</v>
+        <v>1.2153749465942383</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.2153749465942383</v>
+        <v>1.202894926071167</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.202894926071167</v>
+        <v>1.1802921295166016</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.1802921295166016</v>
+        <v>1.1334540843963623</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.1334540843963623</v>
+        <v>1.165252923965454</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -510,25 +510,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.2382765788284377</v>
+        <v>0.23827657882843345</v>
       </c>
       <c r="C2">
-        <v>0.3401243944097631</v>
+        <v>0.3401243944097594</v>
       </c>
       <c r="D2">
-        <v>0.7005571571599043</v>
+        <v>0.7005571571598995</v>
       </c>
       <c r="E2">
-        <v>0.48357942327775794</v>
+        <v>0.48357942327776104</v>
       </c>
       <c r="F2">
-        <v>0.34130176429494075</v>
+        <v>0.3413017642949309</v>
       </c>
       <c r="G2">
-        <v>0.6981404837465992</v>
+        <v>0.6981404837466069</v>
       </c>
       <c r="H2">
-        <v>0.48508934243115887</v>
+        <v>0.485089342431154</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -536,25 +536,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.062410691136134934</v>
+        <v>0.06241069113612469</v>
       </c>
       <c r="C3">
-        <v>0.5385498512551414</v>
+        <v>0.538549851255146</v>
       </c>
       <c r="D3">
-        <v>0.11588656275863954</v>
+        <v>0.11588656275861954</v>
       </c>
       <c r="E3">
-        <v>0.9077424453047895</v>
+        <v>0.9077424453048053</v>
       </c>
       <c r="F3">
-        <v>0.5419638756835667</v>
+        <v>0.54196387568357</v>
       </c>
       <c r="G3">
-        <v>0.11515655182260578</v>
+        <v>0.1151565518225862</v>
       </c>
       <c r="H3">
-        <v>0.9083210361240446</v>
+        <v>0.9083210361240601</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -588,22 +588,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-1.481369736057122</v>
+        <v>-1.4813697360571243</v>
       </c>
       <c r="C5">
-        <v>0.32732483490271075</v>
+        <v>0.3273248349027086</v>
       </c>
       <c r="D5">
-        <v>-4.5256869571092055</v>
+        <v>-4.525686957109242</v>
       </c>
       <c r="E5">
         <v>6.019963505909942e-6</v>
       </c>
       <c r="F5">
-        <v>0.32758816676815483</v>
+        <v>0.327588166768141</v>
       </c>
       <c r="G5">
-        <v>-4.522048982024241</v>
+        <v>-4.522048982024439</v>
       </c>
       <c r="H5">
         <v>6.124388229888922e-6</v>
@@ -614,22 +614,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>-0.023192676241973697</v>
+        <v>-0.02319267624197369</v>
       </c>
       <c r="C6">
-        <v>0.002688561272592905</v>
+        <v>0.002688561272592897</v>
       </c>
       <c r="D6">
-        <v>-8.6264265123503</v>
+        <v>-8.626426512350323</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.0026519084565446334</v>
+        <v>0.002651908456544618</v>
       </c>
       <c r="G6">
-        <v>-8.745654920605043</v>
+        <v>-8.74565492060509</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -640,13 +640,13 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>-0.058755939179560825</v>
+        <v>-0.05875593917956084</v>
       </c>
       <c r="C7">
         <v>0.0014868312568994655</v>
       </c>
       <c r="D7">
-        <v>-39.51755715849448</v>
+        <v>-39.51755715849449</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -655,7 +655,7 @@
         <v>0.001487222829613258</v>
       </c>
       <c r="G7">
-        <v>-39.507152532643616</v>
+        <v>-39.50715253264362</v>
       </c>
       <c r="H7">
         <v>0.0</v>
@@ -666,22 +666,22 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>0.40955972744018193</v>
+        <v>0.40955972744018226</v>
       </c>
       <c r="C8">
-        <v>0.05218048828190325</v>
+        <v>0.052180488281903255</v>
       </c>
       <c r="D8">
-        <v>7.848905614442509</v>
+        <v>7.848905614442514</v>
       </c>
       <c r="E8">
         <v>4.218847493575595e-15</v>
       </c>
       <c r="F8">
-        <v>0.050411010381451134</v>
+        <v>0.05041101038145114</v>
       </c>
       <c r="G8">
-        <v>8.124410210013972</v>
+        <v>8.124410210013977</v>
       </c>
       <c r="H8">
         <v>4.440892098500626e-16</v>
@@ -718,22 +718,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>-0.019483370017356262</v>
+        <v>-0.019483370017356248</v>
       </c>
       <c r="C10">
-        <v>0.002587428446785324</v>
+        <v>0.0025874284467852994</v>
       </c>
       <c r="D10">
-        <v>-7.530013068211727</v>
+        <v>-7.530013068211794</v>
       </c>
       <c r="E10">
         <v>5.062616992290714e-14</v>
       </c>
       <c r="F10">
-        <v>0.002624332849058613</v>
+        <v>0.002624332849058559</v>
       </c>
       <c r="G10">
-        <v>-7.424123058302317</v>
+        <v>-7.424123058302464</v>
       </c>
       <c r="H10">
         <v>1.13464793116691e-13</v>
@@ -744,22 +744,22 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>-0.0173684616394181</v>
+        <v>-0.017368461639418083</v>
       </c>
       <c r="C11">
-        <v>0.0014518522823892986</v>
+        <v>0.0014518522823893099</v>
       </c>
       <c r="D11">
-        <v>-11.962967479608187</v>
+        <v>-11.962967479608082</v>
       </c>
       <c r="E11">
         <v>0.0</v>
       </c>
       <c r="F11">
-        <v>0.0014593078049753678</v>
+        <v>0.0014593078049753535</v>
       </c>
       <c r="G11">
-        <v>-11.901849342682896</v>
+        <v>-11.901849342683</v>
       </c>
       <c r="H11">
         <v>0.0</v>
@@ -770,22 +770,22 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>-0.011602185078949608</v>
+        <v>-0.011602185078949619</v>
       </c>
       <c r="C12">
-        <v>0.000653223991431487</v>
+        <v>0.0006532239914314861</v>
       </c>
       <c r="D12">
-        <v>-17.761419101469876</v>
+        <v>-17.761419101469915</v>
       </c>
       <c r="E12">
         <v>0.0</v>
       </c>
       <c r="F12">
-        <v>0.0006750625436175511</v>
+        <v>0.0006750625436175515</v>
       </c>
       <c r="G12">
-        <v>-17.186829855461056</v>
+        <v>-17.18682985546106</v>
       </c>
       <c r="H12">
         <v>0.0</v>
@@ -796,22 +796,22 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>-0.00636493078980978</v>
+        <v>-0.0063649307898097866</v>
       </c>
       <c r="C13">
-        <v>0.0017041232151145777</v>
+        <v>0.001704123215114567</v>
       </c>
       <c r="D13">
-        <v>-3.735017945508025</v>
+        <v>-3.735017945508052</v>
       </c>
       <c r="E13">
         <v>0.00018770180190541552</v>
       </c>
       <c r="F13">
-        <v>0.0016703763377418199</v>
+        <v>0.0016703763377417685</v>
       </c>
       <c r="G13">
-        <v>-3.810477103869014</v>
+        <v>-3.810477103869135</v>
       </c>
       <c r="H13">
         <v>0.00013869885811246263</v>
@@ -822,22 +822,22 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>0.9375554705923212</v>
+        <v>0.9375554705923215</v>
       </c>
       <c r="C14">
-        <v>0.05298094555389318</v>
+        <v>0.05298094555389319</v>
       </c>
       <c r="D14">
-        <v>17.69608791973376</v>
+        <v>17.696087919733763</v>
       </c>
       <c r="E14">
         <v>0.0</v>
       </c>
       <c r="F14">
-        <v>0.05181026595238339</v>
+        <v>0.05181026595238341</v>
       </c>
       <c r="G14">
-        <v>18.09594012611301</v>
+        <v>18.095940126113007</v>
       </c>
       <c r="H14">
         <v>0.0</v>
@@ -858,7 +858,7 @@
         <v>21</v>
       </c>
       <c r="B1">
-        <v>-5598.900604665885</v>
+        <v>-5598.900604665884</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.165252923965454</v>
+        <v>1.2115840911865234</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -922,7 +922,7 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>11219.80120933177</v>
+        <v>11219.801209331768</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -930,7 +930,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>11295.191529040183</v>
+        <v>11295.191529040181</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -938,7 +938,7 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>0.31687572249032847</v>
+        <v>0.3168757224903286</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MNL_modeChoice_SP.xlsx
+++ b/examples/output/MNL_modeChoice_SP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.2115840911865234</v>
+        <v>1.1915168762207031</v>
       </c>
     </row>
     <row r="7" spans="1:2">
